--- a/自考本科/承办主考学校/主考学校对比.xlsx
+++ b/自考本科/承办主考学校/主考学校对比.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>深圳大学</t>
   </si>
@@ -69,12 +69,18 @@
     <t>一月、六月</t>
   </si>
   <si>
+    <t>三月、九月</t>
+  </si>
+  <si>
+    <t>三月、八月</t>
+  </si>
+  <si>
+    <t>六月、十二月</t>
+  </si>
+  <si>
     <t>三月、？</t>
   </si>
   <si>
-    <t>六月、十二月</t>
-  </si>
-  <si>
     <t>四月、？</t>
   </si>
   <si>
@@ -84,18 +90,18 @@
     <t>考试时间</t>
   </si>
   <si>
-    <t>三月、八月</t>
+    <t>四月、十月</t>
+  </si>
+  <si>
+    <t>五月、十月</t>
+  </si>
+  <si>
+    <t>十月、明年四月</t>
   </si>
   <si>
     <t>五月、？</t>
   </si>
   <si>
-    <t>四月、十月</t>
-  </si>
-  <si>
-    <t>十月、明年四月</t>
-  </si>
-  <si>
     <t>？、九月</t>
   </si>
   <si>
@@ -183,6 +189,9 @@
     <t>笔试平均分要求</t>
   </si>
   <si>
+    <t>60（无分数要求）</t>
+  </si>
+  <si>
     <t>毕业论文成绩要求</t>
   </si>
   <si>
@@ -211,9 +220,6 @@
   </si>
   <si>
     <t>信息发布在两个网站，信息过于分散没有以附件的形式发布</t>
-  </si>
-  <si>
-    <t>没有学位相关公告，没有学士学位授予工作细则</t>
   </si>
   <si>
     <t>过于简洁</t>
@@ -227,6 +233,12 @@
   </si>
   <si>
     <t>实践考试材料提交经常只在要提交的前一天才发公告</t>
+  </si>
+  <si>
+    <t xml:space="preserve">第六条 学生通过高等教育自学考试统考课程视为达到学校学
+位主干课程及学位课程水平统一考试要求。各专业主干课程、学位
+课程(1门外国语、1门专业基础课、2门专业课),由继续教育学
+院确定,报本科生院备案后予以公布。</t>
   </si>
   <si>
     <t xml:space="preserve">实践考试不能一次考五科
@@ -369,7 +381,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -424,9 +436,6 @@
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="1" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -940,10 +949,10 @@
       <c r="C1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="4" t="s">
@@ -1047,143 +1056,143 @@
         <v>17</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" ht="15.75">
       <c r="A5" s="7"/>
       <c r="B5" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" ht="15.75">
       <c r="A6" s="7"/>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" ht="15.75">
       <c r="A7" s="7"/>
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>30</v>
-      </c>
       <c r="J7" s="9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K7" s="1"/>
     </row>
     <row r="8" ht="31.5">
       <c r="A8" s="7"/>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K8" s="1"/>
     </row>
@@ -1201,7 +1210,7 @@
     <row r="10" s="11" customFormat="1" ht="9.5500000000000007" customHeight="1">
       <c r="A10" s="12"/>
       <c r="B10" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C10" s="13"/>
       <c r="D10" s="13" t="s">
@@ -1227,7 +1236,7 @@
     <row r="11" s="11" customFormat="1" ht="9.5500000000000007" customHeight="1">
       <c r="A11" s="12"/>
       <c r="B11" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
@@ -1248,7 +1257,7 @@
     <row r="12" s="11" customFormat="1" ht="9.5500000000000007" customHeight="1">
       <c r="A12" s="12"/>
       <c r="B12" s="13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>13</v>
@@ -1269,22 +1278,22 @@
     </row>
     <row r="13" s="14" customFormat="1" ht="15.75">
       <c r="A13" s="15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="16" t="s">
-        <v>43</v>
+      <c r="D13" s="17" t="s">
+        <v>45</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>47</v>
       </c>
       <c r="G13" s="16" t="s">
         <v>14</v>
@@ -1308,7 +1317,7 @@
     <row r="14" s="1" customFormat="1" ht="15.75">
       <c r="A14" s="7"/>
       <c r="B14" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C14" s="2">
         <v>1500</v>
@@ -1319,10 +1328,10 @@
       <c r="E14" s="2">
         <v>1500</v>
       </c>
-      <c r="F14" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G14" s="8">
+      <c r="F14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="2">
         <v>800</v>
       </c>
       <c r="H14" s="2">
@@ -1332,7 +1341,7 @@
         <v>1000</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -1344,13 +1353,13 @@
     <row r="15" s="1" customFormat="1" ht="15.75">
       <c r="A15" s="7"/>
       <c r="B15" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -1368,7 +1377,7 @@
     <row r="16" s="1" customFormat="1" ht="15.75">
       <c r="A16" s="7"/>
       <c r="B16" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>10</v>
@@ -1379,8 +1388,8 @@
       <c r="E16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="9" t="s">
-        <v>30</v>
+      <c r="F16" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>11</v>
@@ -1403,10 +1412,10 @@
     <row r="17" s="1" customFormat="1" ht="15.75">
       <c r="A17" s="7"/>
       <c r="B17" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D17" s="18"/>
       <c r="E17" s="18"/>
@@ -1421,24 +1430,24 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" s="14" customFormat="1" ht="15.75">
+    <row r="18" s="14" customFormat="1" ht="31.5">
       <c r="A18" s="15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="17">
-        <v>60</v>
+        <v>56</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>57</v>
       </c>
       <c r="D18" s="16">
         <v>70</v>
       </c>
-      <c r="E18" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>30</v>
+      <c r="E18" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" s="16">
+        <v>70</v>
       </c>
       <c r="G18" s="16">
         <v>65</v>
@@ -1462,37 +1471,37 @@
     <row r="19" ht="15.75">
       <c r="A19" s="7"/>
       <c r="B19" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="8">
+        <v>58</v>
+      </c>
+      <c r="C19" s="2">
         <v>70</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="2">
         <v>70</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F19" s="2">
         <v>70</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" ht="15.75">
       <c r="A20" s="7"/>
       <c r="B20" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>13</v>
@@ -1503,8 +1512,8 @@
       <c r="E20" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F20" s="9" t="s">
-        <v>30</v>
+      <c r="F20" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>13</v>
@@ -1513,7 +1522,7 @@
         <v>13</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>13</v>
@@ -1522,7 +1531,7 @@
     <row r="21" ht="15.75">
       <c r="A21" s="7"/>
       <c r="B21" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C21" s="2">
         <v>20</v>
@@ -1530,14 +1539,14 @@
       <c r="D21" s="2">
         <v>30</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="2">
         <v>30</v>
       </c>
       <c r="F21" s="10">
         <v>10</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H21" s="2">
         <v>25</v>
@@ -1569,8 +1578,8 @@
       <c r="E22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>30</v>
+      <c r="F22" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>10</v>
@@ -1582,13 +1591,13 @@
         <v>10</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" s="14" customFormat="1" ht="15.75">
       <c r="A23" s="16"/>
       <c r="B23" s="16" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>14</v>
@@ -1623,23 +1632,21 @@
     <row r="24" s="1" customFormat="1" ht="63">
       <c r="A24" s="2"/>
       <c r="B24" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="2" t="s">
-        <v>65</v>
-      </c>
+      <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -1648,25 +1655,27 @@
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
     </row>
-    <row r="25" s="1" customFormat="1" ht="94.5">
+    <row r="25" s="1" customFormat="1" ht="252">
       <c r="A25" s="2"/>
       <c r="B25" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
+      <c r="E25" s="2" t="s">
+        <v>72</v>
+      </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="1"/>
@@ -1679,21 +1688,21 @@
     <row r="26" s="1" customFormat="1" ht="47.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
@@ -1706,23 +1715,23 @@
     <row r="27" ht="126">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/自考本科/承办主考学校/主考学校对比.xlsx
+++ b/自考本科/承办主考学校/主考学校对比.xlsx
@@ -334,7 +334,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -345,6 +345,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor theme="0" tint="-0.34998626667073579"/>
       </patternFill>
     </fill>
     <fill>
@@ -381,7 +387,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -401,16 +407,19 @@
     <xf fontId="1" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf fontId="1" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" textRotation="255" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="1" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="1" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -958,16 +967,16 @@
       <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="7" t="s">
         <v>7</v>
       </c>
       <c r="K1" s="3"/>
@@ -977,7 +986,7 @@
       <c r="O1" s="3"/>
     </row>
     <row r="2" ht="15.75">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1015,7 +1024,7 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" ht="15.75">
-      <c r="A3" s="7"/>
+      <c r="A3" s="8"/>
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
@@ -1028,7 +1037,7 @@
       <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="9" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="2" t="s">
@@ -1045,7 +1054,7 @@
       </c>
     </row>
     <row r="4" ht="15.75">
-      <c r="A4" s="7"/>
+      <c r="A4" s="8"/>
       <c r="B4" s="2" t="s">
         <v>15</v>
       </c>
@@ -1075,7 +1084,7 @@
       </c>
     </row>
     <row r="5" ht="15.75">
-      <c r="A5" s="7"/>
+      <c r="A5" s="8"/>
       <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
@@ -1105,7 +1114,7 @@
       </c>
     </row>
     <row r="6" ht="15.75">
-      <c r="A6" s="7"/>
+      <c r="A6" s="8"/>
       <c r="B6" s="2" t="s">
         <v>29</v>
       </c>
@@ -1135,7 +1144,7 @@
       </c>
     </row>
     <row r="7" ht="15.75">
-      <c r="A7" s="7"/>
+      <c r="A7" s="8"/>
       <c r="B7" s="2" t="s">
         <v>33</v>
       </c>
@@ -1157,47 +1166,47 @@
       <c r="H7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="10" t="s">
         <v>32</v>
       </c>
       <c r="K7" s="1"/>
     </row>
     <row r="8" ht="31.5">
-      <c r="A8" s="7"/>
+      <c r="A8" s="8"/>
       <c r="B8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="11" t="s">
         <v>37</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="J8" s="10" t="s">
         <v>32</v>
       </c>
       <c r="K8" s="1"/>
     </row>
     <row r="9" ht="7.0999999999999996" customHeight="1">
-      <c r="A9" s="7"/>
+      <c r="A9" s="8"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -1207,115 +1216,115 @@
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" s="11" customFormat="1" ht="9.5500000000000007" customHeight="1">
-      <c r="A10" s="12"/>
-      <c r="B10" s="13" t="s">
+    <row r="10" s="12" customFormat="1" ht="9.5500000000000007" customHeight="1">
+      <c r="A10" s="13"/>
+      <c r="B10" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-    </row>
-    <row r="11" s="11" customFormat="1" ht="9.5500000000000007" customHeight="1">
-      <c r="A11" s="12"/>
-      <c r="B11" s="13" t="s">
+      <c r="C10" s="14"/>
+      <c r="D10" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+    </row>
+    <row r="11" s="12" customFormat="1" ht="9.5500000000000007" customHeight="1">
+      <c r="A11" s="13"/>
+      <c r="B11" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13">
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14">
         <v>1800</v>
       </c>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-    </row>
-    <row r="12" s="11" customFormat="1" ht="9.5500000000000007" customHeight="1">
-      <c r="A12" s="12"/>
-      <c r="B12" s="13" t="s">
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+    </row>
+    <row r="12" s="12" customFormat="1" ht="9.5500000000000007" customHeight="1">
+      <c r="A12" s="13"/>
+      <c r="B12" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-    </row>
-    <row r="13" s="14" customFormat="1" ht="15.75">
-      <c r="A13" s="15" t="s">
+      <c r="C12" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
+    </row>
+    <row r="13" s="15" customFormat="1" ht="15.75">
+      <c r="A13" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="17" t="s">
+      <c r="F13" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="16" t="s">
+      <c r="H13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="I13" s="16" t="s">
+      <c r="I13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J13" s="16" t="s">
+      <c r="J13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="15.75">
-      <c r="A14" s="7"/>
+      <c r="A14" s="8"/>
       <c r="B14" s="2" t="s">
         <v>48</v>
       </c>
@@ -1351,7 +1360,7 @@
       <c r="P14" s="1"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="15.75">
-      <c r="A15" s="7"/>
+      <c r="A15" s="8"/>
       <c r="B15" s="2" t="s">
         <v>49</v>
       </c>
@@ -1375,7 +1384,7 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="15.75">
-      <c r="A16" s="7"/>
+      <c r="A16" s="8"/>
       <c r="B16" s="2" t="s">
         <v>52</v>
       </c>
@@ -1410,66 +1419,66 @@
       <c r="O16" s="1"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="15.75">
-      <c r="A17" s="7"/>
+      <c r="A17" s="8"/>
       <c r="B17" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" s="14" customFormat="1" ht="31.5">
-      <c r="A18" s="15" t="s">
+    <row r="18" s="15" customFormat="1" ht="31.5">
+      <c r="A18" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="17">
         <v>70</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="17">
         <v>70</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="17">
         <v>65</v>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="17">
         <v>70</v>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="17">
         <v>70</v>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="17">
         <v>60</v>
       </c>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="14"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="15"/>
     </row>
     <row r="19" ht="15.75">
-      <c r="A19" s="7"/>
+      <c r="A19" s="8"/>
       <c r="B19" s="2" t="s">
         <v>58</v>
       </c>
@@ -1479,13 +1488,13 @@
       <c r="D19" s="2">
         <v>70</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="11" t="s">
         <v>59</v>
       </c>
       <c r="F19" s="2">
         <v>70</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="11" t="s">
         <v>59</v>
       </c>
       <c r="H19" s="2" t="s">
@@ -1499,7 +1508,7 @@
       </c>
     </row>
     <row r="20" ht="15.75">
-      <c r="A20" s="7"/>
+      <c r="A20" s="8"/>
       <c r="B20" s="2" t="s">
         <v>62</v>
       </c>
@@ -1521,7 +1530,7 @@
       <c r="H20" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="I20" s="10" t="s">
         <v>32</v>
       </c>
       <c r="J20" s="2" t="s">
@@ -1529,7 +1538,7 @@
       </c>
     </row>
     <row r="21" ht="15.75">
-      <c r="A21" s="7"/>
+      <c r="A21" s="8"/>
       <c r="B21" s="2" t="s">
         <v>63</v>
       </c>
@@ -1542,10 +1551,10 @@
       <c r="E21" s="2">
         <v>30</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="11">
         <v>10</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="10" t="s">
         <v>32</v>
       </c>
       <c r="H21" s="2">
@@ -1565,20 +1574,20 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" ht="15.75">
-      <c r="A22" s="7"/>
+      <c r="A22" s="8"/>
       <c r="B22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="9" t="s">
         <v>11</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="9" t="s">
         <v>11</v>
       </c>
       <c r="G22" s="2" t="s">
@@ -1594,40 +1603,40 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" s="14" customFormat="1" ht="15.75">
-      <c r="A23" s="16"/>
-      <c r="B23" s="16" t="s">
+    <row r="23" s="15" customFormat="1" ht="15.75">
+      <c r="A23" s="17"/>
+      <c r="B23" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="D23" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="16" t="s">
+      <c r="D23" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F23" s="16" t="s">
+      <c r="F23" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="G23" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="H23" s="16" t="s">
+      <c r="G23" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="I23" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="14"/>
+      <c r="I23" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
     </row>
     <row r="24" s="1" customFormat="1" ht="63">
       <c r="A24" s="2"/>

--- a/自考本科/承办主考学校/主考学校对比.xlsx
+++ b/自考本科/承办主考学校/主考学校对比.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t>深圳大学</t>
   </si>
@@ -229,16 +229,13 @@
 经常无法连接</t>
   </si>
   <si>
-    <t>说明1</t>
+    <t>资料说明</t>
   </si>
   <si>
     <t>实践考试材料提交经常只在要提交的前一天才发公告</t>
   </si>
   <si>
-    <t xml:space="preserve">第六条 学生通过高等教育自学考试统考课程视为达到学校学
-位主干课程及学位课程水平统一考试要求。各专业主干课程、学位
-课程(1门外国语、1门专业基础课、2门专业课),由继续教育学
-院确定,报本科生院备案后予以公布。</t>
+    <t xml:space="preserve">第六条 学生通过高等教育自学考试统考课程视为达到学校学位主干课程及学位课程水平统一考试要求。......</t>
   </si>
   <si>
     <t xml:space="preserve">实践考试不能一次考五科
@@ -252,10 +249,11 @@
     <t>没有《广东金融学院成人高等教育本科毕业生学士学位授予工作细则》</t>
   </si>
   <si>
-    <t>说明2</t>
-  </si>
-  <si>
-    <t>从实践课程清单可以看出考试形式</t>
+    <t>实践考试说明</t>
+  </si>
+  <si>
+    <t xml:space="preserve">从实践课程清单可以看出考试形式
+经本人询问，暨南大学的实践考试为闭卷</t>
   </si>
   <si>
     <t>从实践大纲可以考出全部开卷</t>
@@ -267,7 +265,7 @@
     <t>从实践大纲可以考出考试形式、部分开卷</t>
   </si>
   <si>
-    <t>备注</t>
+    <t>说明3</t>
   </si>
   <si>
     <r>
@@ -305,12 +303,19 @@
   <si>
     <t>今年下半年才新开考计算机实践，新学校容易踩坑</t>
   </si>
+  <si>
+    <t xml:space="preserve">1. 2026年自考改革后，多数院校同一科目的实践考试一年有两次，如果只有一次就别报
+2. 毕业论文一定要有导师。直接报主考学校的论文培训即可
+3. 想要学位证但没有达到要求前不要申请毕业。成绩合格但没有达到学位要求的课程可以重复考，毕业论文也是
+4. 尽量选学位要求课程平均分仅60分及格的学校，不要和文科比均分！多一分浪费，少一分受罪(反正考的东西都没什么用)
+</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -326,12 +331,6 @@
       <sz val="8.000000"/>
       <color theme="1"/>
       <name val="等距更纱黑体 SC Light"/>
-    </font>
-    <font>
-      <sz val="8.000000"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -387,7 +386,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -410,7 +409,7 @@
     <xf fontId="1" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="255" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -425,7 +424,7 @@
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="255" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -434,7 +433,7 @@
     <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="255" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -445,6 +444,9 @@
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1639,22 +1641,22 @@
       <c r="O23" s="15"/>
     </row>
     <row r="24" s="1" customFormat="1" ht="63">
-      <c r="A24" s="2"/>
+      <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2" t="s">
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="J24" s="1" t="s">
         <v>69</v>
       </c>
       <c r="K24" s="1"/>
@@ -1664,29 +1666,29 @@
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
     </row>
-    <row r="25" s="1" customFormat="1" ht="252">
-      <c r="A25" s="2"/>
+    <row r="25" s="1" customFormat="1" ht="126">
+      <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2" t="s">
+      <c r="D25" s="1"/>
+      <c r="E25" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2" t="s">
+      <c r="F25" s="1"/>
+      <c r="G25" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="I25" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="J25" s="2"/>
+      <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -1694,61 +1696,114 @@
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
     </row>
-    <row r="26" s="1" customFormat="1" ht="47.25">
-      <c r="A26" s="2"/>
+    <row r="26" s="1" customFormat="1" ht="110.25">
+      <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2" t="s">
+      <c r="C26" s="1"/>
+      <c r="D26" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2" t="s">
+      <c r="F26" s="1"/>
+      <c r="G26" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="H26" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" ht="126">
-      <c r="A27" s="2"/>
+    <row r="27" s="1" customFormat="1" ht="126">
+      <c r="A27" s="1"/>
       <c r="B27" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2" t="s">
+      <c r="E27" s="1"/>
+      <c r="F27" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2" t="s">
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1" t="s">
         <v>85</v>
       </c>
     </row>
+    <row r="28" ht="14.25">
+      <c r="C28" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+    </row>
+    <row r="29" ht="14.25">
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+    </row>
+    <row r="30" ht="14.25">
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+    </row>
+    <row r="31" ht="14.25">
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+    </row>
+    <row r="32" ht="14.25">
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A2:A12"/>
     <mergeCell ref="A13:A17"/>
     <mergeCell ref="C17:J17"/>
     <mergeCell ref="A18:A22"/>
+    <mergeCell ref="C28:J32"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>

--- a/自考本科/承办主考学校/主考学校对比.xlsx
+++ b/自考本科/承办主考学校/主考学校对比.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t>深圳大学</t>
   </si>
@@ -123,7 +123,7 @@
     <t>是（参考教材）</t>
   </si>
   <si>
-    <t>是否开卷考试（能带教材）</t>
+    <t>是否开卷考试（可带教材）</t>
   </si>
   <si>
     <t>全部开卷</t>
@@ -162,25 +162,43 @@
     <t>完成10科即可</t>
   </si>
   <si>
+    <t>论文报名时间</t>
+  </si>
+  <si>
+    <t>四月、十一月</t>
+  </si>
+  <si>
+    <t>一月、八月</t>
+  </si>
+  <si>
+    <t>一月、四月</t>
+  </si>
+  <si>
+    <t>论文成绩公布时间</t>
+  </si>
+  <si>
+    <t>6个月</t>
+  </si>
+  <si>
+    <t>9个月</t>
+  </si>
+  <si>
+    <t>4个月</t>
+  </si>
+  <si>
     <t>论文指导费用</t>
   </si>
   <si>
-    <t>论文完成周期</t>
-  </si>
-  <si>
-    <t>6个月</t>
-  </si>
-  <si>
-    <t>9个月</t>
-  </si>
-  <si>
     <t>毕业论文报考方式</t>
   </si>
   <si>
     <t>毕业申请方式</t>
   </si>
   <si>
-    <t>（统一为广东教育考试院）</t>
+    <t>（统一为广东教育考试院）（申请时间：六月、十二月）</t>
+  </si>
+  <si>
+    <t>学位申请时间</t>
   </si>
   <si>
     <t>学位</t>
@@ -232,7 +250,8 @@
     <t>资料说明</t>
   </si>
   <si>
-    <t>实践考试材料提交经常只在要提交的前一天才发公告</t>
+    <t xml:space="preserve">注意！官网公布报考信息的时间通常非常紧张，往往是开始报考前一天，注意邮寄资料的时间
+实践考试材料提交经常只在要提交的前一天才发公告</t>
   </si>
   <si>
     <t xml:space="preserve">第六条 学生通过高等教育自学考试统考课程视为达到学校学位主干课程及学位课程水平统一考试要求。......</t>
@@ -268,31 +287,7 @@
     <t>说明3</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等距更纱黑体 SC Light"/>
-      </rPr>
-      <t xml:space="preserve">要求最低
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="2"/>
-        <rFont val="等距更纱黑体 SC Light"/>
-      </rPr>
-      <t>注意！</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等距更纱黑体 SC Light"/>
-      </rPr>
-      <t>官网公布报考信息的时间通常非常紧张，往往是开始报考前一天，注意邮寄资料的时间</t>
-    </r>
+    <t>要求最低</t>
   </si>
   <si>
     <t>全程线上提交资料</t>
@@ -302,12 +297,17 @@
   </si>
   <si>
     <t>今年下半年才新开考计算机实践，新学校容易踩坑</t>
+  </si>
+  <si>
+    <t>注：</t>
   </si>
   <si>
     <t xml:space="preserve">1. 2026年自考改革后，多数院校同一科目的实践考试一年有两次，如果只有一次就别报
 2. 毕业论文一定要有导师。直接报主考学校的论文培训即可
 3. 想要学位证但没有达到要求前不要申请毕业。成绩合格但没有达到学位要求的课程可以重复考，毕业论文也是
 4. 尽量选学位要求课程平均分仅60分及格的学校，不要和文科比均分！多一分浪费，少一分受罪(反正考的东西都没什么用)
+5. 学位申请有很强的时间限制，必须在申请毕业后的半年内申请，且学位申请指定毕业时间。如：今年下半年申请毕业，明年上半年就要申请学位（仅此一次）
+6. 
 </t>
   </si>
 </sst>
@@ -315,7 +315,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -331,6 +331,12 @@
       <sz val="8.000000"/>
       <color theme="1"/>
       <name val="等距更纱黑体 SC Light"/>
+    </font>
+    <font>
+      <sz val="48.000000"/>
+      <color indexed="2"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -365,7 +371,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -382,11 +388,100 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="2"/>
+      </left>
+      <right style="none"/>
+      <top style="thick">
+        <color indexed="2"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thick">
+        <color indexed="2"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thick">
+        <color indexed="2"/>
+      </right>
+      <top style="thick">
+        <color indexed="2"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="2"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thick">
+        <color indexed="2"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="2"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thick">
+        <color indexed="2"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thick">
+        <color indexed="2"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thick">
+        <color indexed="2"/>
+      </right>
+      <top style="none"/>
+      <bottom style="thick">
+        <color indexed="2"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="37">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -443,9 +538,57 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="1" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1325,35 +1468,27 @@
       <c r="O13" s="15"/>
       <c r="P13" s="15"/>
     </row>
-    <row r="14" s="1" customFormat="1" ht="15.75">
+    <row r="14" s="15" customFormat="1" ht="15.75">
       <c r="A14" s="8"/>
       <c r="B14" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="2">
-        <v>1500</v>
-      </c>
-      <c r="D14" s="2">
-        <v>1000</v>
-      </c>
-      <c r="E14" s="2">
-        <v>1500</v>
+      <c r="C14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14" s="2">
-        <v>800</v>
-      </c>
-      <c r="H14" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I14" s="2">
-        <v>1000</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>32</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -1364,16 +1499,20 @@
     <row r="15" s="1" customFormat="1" ht="15.75">
       <c r="A15" s="8"/>
       <c r="B15" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+        <v>54</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -1388,422 +1527,549 @@
     <row r="16" s="1" customFormat="1" ht="15.75">
       <c r="A16" s="8"/>
       <c r="B16" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>11</v>
+        <v>56</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1500</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1500</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>11</v>
+        <v>32</v>
+      </c>
+      <c r="G16" s="2">
+        <v>800</v>
+      </c>
+      <c r="H16" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1000</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
+      <c r="P16" s="19"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="15.75">
       <c r="A17" s="8"/>
       <c r="B17" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
+        <v>57</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" s="15" customFormat="1" ht="31.5">
-      <c r="A18" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" s="17">
-        <v>70</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="F18" s="17">
-        <v>70</v>
-      </c>
-      <c r="G18" s="17">
-        <v>65</v>
-      </c>
-      <c r="H18" s="17">
-        <v>70</v>
-      </c>
-      <c r="I18" s="17">
-        <v>70</v>
-      </c>
-      <c r="J18" s="17">
+    <row r="18" s="20" customFormat="1" ht="15.75">
+      <c r="A18" s="21"/>
+      <c r="B18" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+    </row>
+    <row r="19" s="19" customFormat="1" ht="15.75">
+      <c r="A19" s="24"/>
+      <c r="B19" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="15"/>
-      <c r="O18" s="15"/>
-      <c r="P18" s="15"/>
-    </row>
-    <row r="19" ht="15.75">
-      <c r="A19" s="8"/>
-      <c r="B19" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" s="2">
-        <v>70</v>
-      </c>
-      <c r="D19" s="2">
-        <v>70</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="F19" s="2">
-        <v>70</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I19" s="2" t="s">
+      <c r="C19" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="19"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="31.5">
+      <c r="A20" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="J19" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" ht="15.75">
-      <c r="A20" s="8"/>
       <c r="B20" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="C20" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="2">
+        <v>70</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F20" s="2">
+        <v>70</v>
+      </c>
+      <c r="G20" s="2">
+        <v>65</v>
+      </c>
+      <c r="H20" s="2">
+        <v>70</v>
+      </c>
+      <c r="I20" s="2">
+        <v>70</v>
+      </c>
+      <c r="J20" s="2">
+        <v>60</v>
+      </c>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
     </row>
     <row r="21" ht="15.75">
       <c r="A21" s="8"/>
       <c r="B21" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C21" s="2">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="D21" s="2">
-        <v>30</v>
-      </c>
-      <c r="E21" s="2">
-        <v>30</v>
-      </c>
-      <c r="F21" s="11">
-        <v>10</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="H21" s="2">
-        <v>25</v>
-      </c>
-      <c r="I21" s="2">
-        <v>30</v>
-      </c>
-      <c r="J21" s="2">
-        <v>25</v>
-      </c>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
+        <v>70</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F21" s="2">
+        <v>70</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="22" ht="15.75">
       <c r="A22" s="8"/>
       <c r="B22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75">
+      <c r="A23" s="8"/>
+      <c r="B23" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="2">
+        <v>20</v>
+      </c>
+      <c r="D23" s="2">
+        <v>30</v>
+      </c>
+      <c r="E23" s="2">
+        <v>30</v>
+      </c>
+      <c r="F23" s="11">
+        <v>10</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23" s="2">
+        <v>25</v>
+      </c>
+      <c r="I23" s="2">
+        <v>30</v>
+      </c>
+      <c r="J23" s="2">
+        <v>25</v>
+      </c>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" ht="15.75">
+      <c r="A24" s="8"/>
+      <c r="B24" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D24" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F24" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G24" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="H24" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I22" s="2" t="s">
+      <c r="I24" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J22" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" s="15" customFormat="1" ht="15.75">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" s="17" t="s">
+      <c r="J24" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" s="17" customFormat="1" ht="15.75">
+      <c r="A25" s="17"/>
+      <c r="B25" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="D23" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="17" t="s">
+      <c r="D25" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F23" s="17" t="s">
+      <c r="F25" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="G23" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="H23" s="17" t="s">
+      <c r="G25" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="I23" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="15"/>
-      <c r="O23" s="15"/>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="63">
-      <c r="A24" s="1"/>
-      <c r="B24" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="126">
-      <c r="A25" s="1"/>
-      <c r="B25" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1" t="s">
+      <c r="I25" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J25" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+    </row>
+    <row r="26" s="2" customFormat="1" ht="63">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1" t="s">
+      <c r="C26" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="J26" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-    </row>
-    <row r="26" s="1" customFormat="1" ht="110.25">
-      <c r="A26" s="1"/>
-      <c r="B26" s="2" t="s">
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+    </row>
+    <row r="27" s="2" customFormat="1" ht="173.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1" t="s">
+      <c r="C27" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="D27" s="2"/>
+      <c r="E27" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1" t="s">
+      <c r="F27" s="2"/>
+      <c r="G27" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H27" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="126">
-      <c r="A27" s="1"/>
-      <c r="B27" s="2" t="s">
+      <c r="I27" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+    </row>
+    <row r="28" s="2" customFormat="1" ht="110.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="C28" s="2"/>
+      <c r="D28" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1" t="s">
+      <c r="E28" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1" t="s">
+      <c r="F28" s="2"/>
+      <c r="G28" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="28" ht="14.25">
-      <c r="C28" s="20" t="s">
+      <c r="H28" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-    </row>
-    <row r="29" ht="14.25">
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+    </row>
+    <row r="29" s="2" customFormat="1" ht="126">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
     </row>
     <row r="30" ht="14.25">
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
+      <c r="B30" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="30"/>
     </row>
     <row r="31" ht="14.25">
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
+      <c r="J31" s="33"/>
     </row>
     <row r="32" ht="14.25">
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="33"/>
+    </row>
+    <row r="33" ht="14.25">
+      <c r="B33" s="27"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="33"/>
+    </row>
+    <row r="34" ht="14.25">
+      <c r="B34" s="27"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="32"/>
+      <c r="J34" s="33"/>
+    </row>
+    <row r="35" ht="14.25">
+      <c r="B35" s="27"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
+      <c r="J35" s="33"/>
+    </row>
+    <row r="36" ht="14.25">
+      <c r="B36" s="27"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="33"/>
+    </row>
+    <row r="37" ht="14.25">
+      <c r="B37" s="27"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
+      <c r="J37" s="33"/>
+    </row>
+    <row r="38" ht="14.25">
+      <c r="B38" s="27"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="32"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="32"/>
+      <c r="J38" s="33"/>
+    </row>
+    <row r="39" ht="14.25">
+      <c r="B39" s="27"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="35"/>
+      <c r="E39" s="35"/>
+      <c r="F39" s="35"/>
+      <c r="G39" s="35"/>
+      <c r="H39" s="35"/>
+      <c r="I39" s="35"/>
+      <c r="J39" s="36"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A2:A12"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="C17:J17"/>
-    <mergeCell ref="A18:A22"/>
-    <mergeCell ref="C28:J32"/>
+    <mergeCell ref="A13:A18"/>
+    <mergeCell ref="C18:J18"/>
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="B30:B39"/>
+    <mergeCell ref="C30:J39"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>

--- a/自考本科/承办主考学校/主考学校对比.xlsx
+++ b/自考本科/承办主考学校/主考学校对比.xlsx
@@ -371,7 +371,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -383,7 +383,7 @@
       <left style="none"/>
       <right style="none"/>
       <top style="medium">
-        <color theme="1"/>
+        <color theme="1" tint="0"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
@@ -395,6 +395,15 @@
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
@@ -481,7 +490,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -537,21 +546,21 @@
     <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="1" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="1" vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="255" vertical="center" wrapText="1"/>
     </xf>
@@ -561,12 +570,12 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="1" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf fontId="1" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -576,12 +585,12 @@
     <xf fontId="1" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf fontId="1" fillId="0" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf fontId="1" fillId="0" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -589,6 +598,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1093,8 +1105,7 @@
     <col customWidth="1" min="1" max="1" style="1" width="5.00390625"/>
     <col customWidth="1" min="2" max="2" style="2" width="25.421875"/>
     <col customWidth="1" min="3" max="10" style="1" width="17.57421875"/>
-    <col customWidth="1" min="11" max="15" style="1" width="20.7109375"/>
-    <col min="16" max="16384" style="1" width="9.140625"/>
+    <col min="11" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" s="3" customFormat="1" ht="15.75">
@@ -1468,7 +1479,7 @@
       <c r="O13" s="15"/>
       <c r="P13" s="15"/>
     </row>
-    <row r="14" s="15" customFormat="1" ht="15.75">
+    <row r="14" s="1" customFormat="1" ht="15.75">
       <c r="A14" s="8"/>
       <c r="B14" s="2" t="s">
         <v>48</v>
@@ -1558,7 +1569,7 @@
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
-      <c r="P16" s="19"/>
+      <c r="P16" s="1"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="15.75">
       <c r="A17" s="8"/>
@@ -1595,28 +1606,28 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" s="20" customFormat="1" ht="15.75">
-      <c r="A18" s="21"/>
-      <c r="B18" s="22" t="s">
+    <row r="18" s="19" customFormat="1" ht="15.75">
+      <c r="A18" s="20"/>
+      <c r="B18" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-      <c r="M18" s="20"/>
-      <c r="N18" s="20"/>
-      <c r="O18" s="20"/>
-    </row>
-    <row r="19" s="19" customFormat="1" ht="15.75">
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+    </row>
+    <row r="19" s="23" customFormat="1" ht="15.75">
       <c r="A19" s="24"/>
       <c r="B19" s="25" t="s">
         <v>60</v>
@@ -1628,16 +1639,16 @@
       <c r="E19" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="19"/>
+      <c r="F19" s="23"/>
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
       <c r="J19" s="26"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="19"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="23"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
     </row>
     <row r="20" s="1" customFormat="1" ht="31.5">
       <c r="A20" s="8" t="s">
@@ -1803,40 +1814,40 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" s="17" customFormat="1" ht="15.75">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17" t="s">
+    <row r="25" s="27" customFormat="1" ht="15.75">
+      <c r="A25" s="27"/>
+      <c r="B25" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="D25" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="17" t="s">
+      <c r="D25" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="F25" s="17" t="s">
+      <c r="F25" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="G25" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="H25" s="17" t="s">
+      <c r="G25" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="I25" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="J25" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="17"/>
+      <c r="I25" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="J25" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="K25" s="27"/>
+      <c r="L25" s="27"/>
+      <c r="M25" s="27"/>
+      <c r="N25" s="27"/>
+      <c r="O25" s="27"/>
     </row>
     <row r="26" s="2" customFormat="1" ht="63">
       <c r="A26" s="2"/>
@@ -1949,118 +1960,118 @@
       <c r="O29" s="2"/>
     </row>
     <row r="30" ht="14.25">
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="C30" s="28" t="s">
+      <c r="C30" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="31"/>
     </row>
     <row r="31" ht="14.25">
-      <c r="B31" s="27"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
-      <c r="J31" s="33"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
+      <c r="J31" s="34"/>
     </row>
     <row r="32" ht="14.25">
-      <c r="B32" s="27"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="32"/>
-      <c r="J32" s="33"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="34"/>
     </row>
     <row r="33" ht="14.25">
-      <c r="B33" s="27"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="33"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="34"/>
     </row>
     <row r="34" ht="14.25">
-      <c r="B34" s="27"/>
-      <c r="C34" s="31"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="32"/>
-      <c r="J34" s="33"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="33"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="33"/>
+      <c r="I34" s="33"/>
+      <c r="J34" s="34"/>
     </row>
     <row r="35" ht="14.25">
-      <c r="B35" s="27"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="32"/>
-      <c r="I35" s="32"/>
-      <c r="J35" s="33"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="33"/>
+      <c r="G35" s="33"/>
+      <c r="H35" s="33"/>
+      <c r="I35" s="33"/>
+      <c r="J35" s="34"/>
     </row>
     <row r="36" ht="14.25">
-      <c r="B36" s="27"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="32"/>
-      <c r="J36" s="33"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="34"/>
     </row>
     <row r="37" ht="14.25">
-      <c r="B37" s="27"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="32"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32"/>
-      <c r="I37" s="32"/>
-      <c r="J37" s="33"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="33"/>
+      <c r="E37" s="33"/>
+      <c r="F37" s="33"/>
+      <c r="G37" s="33"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="33"/>
+      <c r="J37" s="34"/>
     </row>
     <row r="38" ht="14.25">
-      <c r="B38" s="27"/>
-      <c r="C38" s="31"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="32"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="32"/>
-      <c r="I38" s="32"/>
-      <c r="J38" s="33"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="33"/>
+      <c r="H38" s="33"/>
+      <c r="I38" s="33"/>
+      <c r="J38" s="34"/>
     </row>
     <row r="39" ht="14.25">
-      <c r="B39" s="27"/>
-      <c r="C39" s="34"/>
-      <c r="D39" s="35"/>
-      <c r="E39" s="35"/>
-      <c r="F39" s="35"/>
-      <c r="G39" s="35"/>
-      <c r="H39" s="35"/>
-      <c r="I39" s="35"/>
-      <c r="J39" s="36"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="35"/>
+      <c r="D39" s="36"/>
+      <c r="E39" s="36"/>
+      <c r="F39" s="36"/>
+      <c r="G39" s="36"/>
+      <c r="H39" s="36"/>
+      <c r="I39" s="36"/>
+      <c r="J39" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/自考本科/承办主考学校/主考学校对比.xlsx
+++ b/自考本科/承办主考学校/主考学校对比.xlsx
@@ -201,6 +201,9 @@
     <t>学位申请时间</t>
   </si>
   <si>
+    <t>五月、十一月</t>
+  </si>
+  <si>
     <t>学位</t>
   </si>
   <si>
@@ -293,16 +296,14 @@
     <t>全程线上提交资料</t>
   </si>
   <si>
-    <t>理论毕业时间最短</t>
-  </si>
-  <si>
     <t>今年下半年才新开考计算机实践，新学校容易踩坑</t>
   </si>
   <si>
     <t>注：</t>
   </si>
   <si>
-    <t xml:space="preserve">1. 2026年自考改革后，多数院校同一科目的实践考试一年有两次，如果只有一次就别报
+    <t xml:space="preserve">0. 理论最快一年零二个月考完申请毕业（选华南理工大学，26年4月首考，27年6月申请毕业）
+1. 2026年自考改革后，多数院校同一科目的实践考试一年有两次，如果只有一次就别报
 2. 毕业论文一定要有导师。直接报主考学校的论文培训即可
 3. 想要学位证但没有达到要求前不要申请毕业。成绩合格但没有达到学位要求的课程可以重复考，毕业论文也是
 4. 尽量选学位要求课程平均分仅60分及格的学校，不要和文科比均分！多一分浪费，少一分受罪(反正考的东西都没什么用)
@@ -490,7 +491,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="35">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -557,15 +558,6 @@
     </xf>
     <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1" vertical="center" wrapText="1"/>
@@ -1627,44 +1619,44 @@
       <c r="N18" s="19"/>
       <c r="O18" s="19"/>
     </row>
-    <row r="19" s="23" customFormat="1" ht="15.75">
-      <c r="A19" s="24"/>
-      <c r="B19" s="25" t="s">
+    <row r="19" s="1" customFormat="1" ht="15.75">
+      <c r="A19" s="8"/>
+      <c r="B19" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26" t="s">
+      <c r="C19" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="23"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="23"/>
-      <c r="L19" s="23"/>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
     </row>
     <row r="20" s="1" customFormat="1" ht="31.5">
       <c r="A20" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D20" s="2">
         <v>70</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F20" s="2">
         <v>70</v>
@@ -1691,7 +1683,7 @@
     <row r="21" ht="15.75">
       <c r="A21" s="8"/>
       <c r="B21" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C21" s="2">
         <v>70</v>
@@ -1700,28 +1692,28 @@
         <v>70</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F21" s="2">
         <v>70</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" ht="15.75">
       <c r="A22" s="8"/>
       <c r="B22" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>13</v>
@@ -1751,7 +1743,7 @@
     <row r="23" ht="15.75">
       <c r="A23" s="8"/>
       <c r="B23" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C23" s="2">
         <v>20</v>
@@ -1811,51 +1803,51 @@
         <v>10</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" s="27" customFormat="1" ht="15.75">
-      <c r="A25" s="27"/>
-      <c r="B25" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="C25" s="27" t="s">
+    </row>
+    <row r="25" s="24" customFormat="1" ht="15.75">
+      <c r="A25" s="24"/>
+      <c r="B25" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="D25" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="27" t="s">
+      <c r="D25" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="F25" s="27" t="s">
+      <c r="F25" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="G25" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="H25" s="27" t="s">
+      <c r="G25" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="I25" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="J25" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="K25" s="27"/>
-      <c r="L25" s="27"/>
-      <c r="M25" s="27"/>
-      <c r="N25" s="27"/>
-      <c r="O25" s="27"/>
+      <c r="I25" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="J25" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="K25" s="24"/>
+      <c r="L25" s="24"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
     </row>
     <row r="26" s="2" customFormat="1" ht="63">
       <c r="A26" s="2"/>
       <c r="B26" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
@@ -1863,10 +1855,10 @@
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
@@ -1878,24 +1870,24 @@
     <row r="27" s="2" customFormat="1" ht="173.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -1908,21 +1900,21 @@
     <row r="28" s="2" customFormat="1" ht="110.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
@@ -1932,21 +1924,19 @@
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
     </row>
-    <row r="29" s="2" customFormat="1" ht="126">
+    <row r="29" s="2" customFormat="1" ht="63">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E29" s="2"/>
-      <c r="F29" s="2" t="s">
-        <v>90</v>
-      </c>
+      <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
@@ -1960,118 +1950,118 @@
       <c r="O29" s="2"/>
     </row>
     <row r="30" ht="14.25">
-      <c r="B30" s="28" t="s">
+      <c r="B30" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="C30" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="30"/>
-      <c r="I30" s="30"/>
-      <c r="J30" s="31"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="28"/>
     </row>
     <row r="31" ht="14.25">
-      <c r="B31" s="28"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="33"/>
-      <c r="J31" s="34"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="31"/>
     </row>
     <row r="32" ht="14.25">
-      <c r="B32" s="28"/>
-      <c r="C32" s="32"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="33"/>
-      <c r="J32" s="34"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="31"/>
     </row>
     <row r="33" ht="14.25">
-      <c r="B33" s="28"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
-      <c r="J33" s="34"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="31"/>
     </row>
     <row r="34" ht="14.25">
-      <c r="B34" s="28"/>
-      <c r="C34" s="32"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="33"/>
-      <c r="G34" s="33"/>
-      <c r="H34" s="33"/>
-      <c r="I34" s="33"/>
-      <c r="J34" s="34"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="31"/>
     </row>
     <row r="35" ht="14.25">
-      <c r="B35" s="28"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="33"/>
-      <c r="E35" s="33"/>
-      <c r="F35" s="33"/>
-      <c r="G35" s="33"/>
-      <c r="H35" s="33"/>
-      <c r="I35" s="33"/>
-      <c r="J35" s="34"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="31"/>
     </row>
     <row r="36" ht="14.25">
-      <c r="B36" s="28"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="33"/>
-      <c r="J36" s="34"/>
+      <c r="B36" s="25"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="31"/>
     </row>
     <row r="37" ht="14.25">
-      <c r="B37" s="28"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
-      <c r="J37" s="34"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="31"/>
     </row>
     <row r="38" ht="14.25">
-      <c r="B38" s="28"/>
-      <c r="C38" s="32"/>
-      <c r="D38" s="33"/>
-      <c r="E38" s="33"/>
-      <c r="F38" s="33"/>
-      <c r="G38" s="33"/>
-      <c r="H38" s="33"/>
-      <c r="I38" s="33"/>
-      <c r="J38" s="34"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="31"/>
     </row>
     <row r="39" ht="14.25">
-      <c r="B39" s="28"/>
-      <c r="C39" s="35"/>
-      <c r="D39" s="36"/>
-      <c r="E39" s="36"/>
-      <c r="F39" s="36"/>
-      <c r="G39" s="36"/>
-      <c r="H39" s="36"/>
-      <c r="I39" s="36"/>
-      <c r="J39" s="37"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="33"/>
+      <c r="E39" s="33"/>
+      <c r="F39" s="33"/>
+      <c r="G39" s="33"/>
+      <c r="H39" s="33"/>
+      <c r="I39" s="33"/>
+      <c r="J39" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/自考本科/承办主考学校/主考学校对比.xlsx
+++ b/自考本科/承办主考学校/主考学校对比.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t>深圳大学</t>
   </si>
@@ -184,6 +184,9 @@
   </si>
   <si>
     <t>4个月</t>
+  </si>
+  <si>
+    <t>论文培训报名时间</t>
   </si>
   <si>
     <t>论文指导费用</t>
@@ -302,14 +305,38 @@
     <t>注：</t>
   </si>
   <si>
-    <t xml:space="preserve">0. 理论最快一年零二个月考完申请毕业（选华南理工大学，26年4月首考，27年6月申请毕业）
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等距更纱黑体 SC Light"/>
+      </rPr>
+      <t xml:space="preserve">0. 理论最快一年零二个月考完申请毕业（选华南理工大学，26年4月首考，27年6月申请毕业）
 1. 2026年自考改革后，多数院校同一科目的实践考试一年有两次，如果只有一次就别报
-2. 毕业论文一定要有导师。直接报主考学校的论文培训即可
+</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等距更纱黑体 SC Light"/>
+      </rPr>
+      <t xml:space="preserve">2. 毕业论文一定要有导师。直接报主考学校的论文培训即可</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等距更纱黑体 SC Light"/>
+      </rPr>
+      <t xml:space="preserve">
 3. 想要学位证但没有达到要求前不要申请毕业。成绩合格但没有达到学位要求的课程可以重复考，毕业论文也是
 4. 尽量选学位要求课程平均分仅60分及格的学校，不要和文科比均分！多一分浪费，少一分受罪(反正考的东西都没什么用)
 5. 学位申请有很强的时间限制，必须在申请毕业后的半年内申请，且学位申请指定毕业时间。如：今年下半年申请毕业，明年上半年就要申请学位（仅此一次）
 6. 
 </t>
+    </r>
   </si>
 </sst>
 </file>
@@ -383,19 +410,19 @@
     <border>
       <left style="none"/>
       <right style="none"/>
-      <top style="medium">
-        <color theme="1" tint="0"/>
-      </top>
-      <bottom style="none"/>
+      <top style="none"/>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
       <right style="none"/>
-      <top style="none"/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
+      <top style="medium">
+        <color theme="1" tint="0"/>
+      </top>
+      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
@@ -499,19 +526,19 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="1" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="1" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="1" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="1" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -535,6 +562,18 @@
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -544,19 +583,7 @@
     <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1532,30 +1559,18 @@
       <c r="B16" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="2">
-        <v>1500</v>
-      </c>
-      <c r="D16" s="2">
-        <v>1000</v>
-      </c>
-      <c r="E16" s="2">
-        <v>1500</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" s="2">
-        <v>800</v>
-      </c>
-      <c r="H16" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I16" s="2">
-        <v>1000</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="C16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -1568,176 +1583,182 @@
       <c r="B17" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>11</v>
+      <c r="C17" s="2">
+        <v>1500</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1500</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>11</v>
+        <v>32</v>
+      </c>
+      <c r="G17" s="2">
+        <v>800</v>
+      </c>
+      <c r="H17" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I17" s="2">
+        <v>1000</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
-    </row>
-    <row r="18" s="19" customFormat="1" ht="15.75">
-      <c r="A18" s="20"/>
-      <c r="B18" s="21" t="s">
+      <c r="P17" s="1"/>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="15.75">
+      <c r="A18" s="8"/>
+      <c r="B18" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+    </row>
+    <row r="19" s="19" customFormat="1" ht="15.75">
+      <c r="A19" s="20"/>
+      <c r="B19" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="15.75">
-      <c r="A19" s="8"/>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="15.75">
+      <c r="A20" s="8"/>
+      <c r="B20" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23" t="s">
+      <c r="C20" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="1"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
-      <c r="I19" s="23"/>
-      <c r="J19" s="23"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-    </row>
-    <row r="20" s="1" customFormat="1" ht="31.5">
-      <c r="A20" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" s="2">
-        <v>70</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F20" s="2">
-        <v>70</v>
-      </c>
-      <c r="G20" s="2">
-        <v>65</v>
-      </c>
-      <c r="H20" s="2">
-        <v>70</v>
-      </c>
-      <c r="I20" s="2">
-        <v>70</v>
-      </c>
-      <c r="J20" s="2">
-        <v>60</v>
-      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="23"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-    </row>
-    <row r="21" ht="15.75">
-      <c r="A21" s="8"/>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="31.5">
+      <c r="A21" s="8" t="s">
+        <v>63</v>
+      </c>
       <c r="B21" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>65</v>
-      </c>
-      <c r="C21" s="2">
-        <v>70</v>
       </c>
       <c r="D21" s="2">
         <v>70</v>
       </c>
-      <c r="E21" s="11" t="s">
-        <v>66</v>
+      <c r="E21" s="9" t="s">
+        <v>65</v>
       </c>
       <c r="F21" s="2">
         <v>70</v>
       </c>
-      <c r="G21" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>68</v>
-      </c>
+      <c r="G21" s="2">
+        <v>65</v>
+      </c>
+      <c r="H21" s="2">
+        <v>70</v>
+      </c>
+      <c r="I21" s="2">
+        <v>70</v>
+      </c>
+      <c r="J21" s="2">
+        <v>60</v>
+      </c>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
     </row>
     <row r="22" ht="15.75">
       <c r="A22" s="8"/>
       <c r="B22" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="2">
+        <v>70</v>
+      </c>
+      <c r="D22" s="2">
+        <v>70</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F22" s="2">
+        <v>70</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>32</v>
-      </c>
       <c r="J22" s="2" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" ht="15.75">
@@ -1745,151 +1766,151 @@
       <c r="B23" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C23" s="2">
-        <v>20</v>
-      </c>
-      <c r="D23" s="2">
-        <v>30</v>
-      </c>
-      <c r="E23" s="2">
-        <v>30</v>
-      </c>
-      <c r="F23" s="11">
-        <v>10</v>
-      </c>
-      <c r="G23" s="10" t="s">
+      <c r="C23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="H23" s="2">
-        <v>25</v>
-      </c>
-      <c r="I23" s="2">
-        <v>30</v>
-      </c>
-      <c r="J23" s="2">
-        <v>25</v>
-      </c>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
+      <c r="J23" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="24" ht="15.75">
       <c r="A24" s="8"/>
       <c r="B24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="2">
+        <v>20</v>
+      </c>
+      <c r="D24" s="2">
+        <v>30</v>
+      </c>
+      <c r="E24" s="2">
+        <v>30</v>
+      </c>
+      <c r="F24" s="11">
+        <v>10</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24" s="2">
+        <v>25</v>
+      </c>
+      <c r="I24" s="2">
+        <v>30</v>
+      </c>
+      <c r="J24" s="2">
+        <v>25</v>
+      </c>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" ht="15.75">
+      <c r="A25" s="8"/>
+      <c r="B25" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D25" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F25" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G25" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H25" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I24" s="2" t="s">
+      <c r="I25" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J24" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" s="24" customFormat="1" ht="15.75">
-      <c r="A25" s="24"/>
-      <c r="B25" s="24" t="s">
+      <c r="J25" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="24" t="s">
+    </row>
+    <row r="26" s="24" customFormat="1" ht="15.75">
+      <c r="A26" s="24"/>
+      <c r="B26" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="D25" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="24" t="s">
+      <c r="D26" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="F25" s="24" t="s">
+      <c r="F26" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="G25" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="H25" s="24" t="s">
+      <c r="G26" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="I25" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="J25" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-    </row>
-    <row r="26" s="2" customFormat="1" ht="63">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-      <c r="P26" s="2"/>
-    </row>
-    <row r="27" s="2" customFormat="1" ht="173.25">
+      <c r="I26" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="J26" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="K26" s="24"/>
+      <c r="L26" s="24"/>
+      <c r="M26" s="24"/>
+      <c r="N26" s="24"/>
+      <c r="O26" s="24"/>
+    </row>
+    <row r="27" s="2" customFormat="1" ht="63">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="J27" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="J27" s="2"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -1897,83 +1918,102 @@
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
     </row>
-    <row r="28" s="2" customFormat="1" ht="110.25">
+    <row r="28" s="2" customFormat="1" ht="173.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2" t="s">
-        <v>84</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" s="2"/>
       <c r="E28" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I28" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
-    </row>
-    <row r="29" s="2" customFormat="1" ht="63">
+      <c r="P28" s="2"/>
+    </row>
+    <row r="29" s="2" customFormat="1" ht="110.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
       <c r="I29" s="2"/>
-      <c r="J29" s="2" t="s">
-        <v>91</v>
-      </c>
+      <c r="J29" s="2"/>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
     </row>
-    <row r="30" ht="14.25">
-      <c r="B30" s="25" t="s">
+    <row r="30" s="2" customFormat="1" ht="63">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C30" s="26" t="s">
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+    </row>
+    <row r="31" ht="14.25">
+      <c r="B31" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="27"/>
-      <c r="J30" s="28"/>
-    </row>
-    <row r="31" ht="14.25">
-      <c r="B31" s="25"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="30"/>
-      <c r="J31" s="31"/>
+      <c r="C31" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="27"/>
+      <c r="J31" s="28"/>
     </row>
     <row r="32" ht="14.25">
       <c r="B32" s="25"/>
@@ -2054,23 +2094,34 @@
     </row>
     <row r="39" ht="14.25">
       <c r="B39" s="25"/>
-      <c r="C39" s="32"/>
-      <c r="D39" s="33"/>
-      <c r="E39" s="33"/>
-      <c r="F39" s="33"/>
-      <c r="G39" s="33"/>
-      <c r="H39" s="33"/>
-      <c r="I39" s="33"/>
-      <c r="J39" s="34"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="31"/>
+    </row>
+    <row r="40" ht="14.25">
+      <c r="B40" s="25"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="33"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="33"/>
+      <c r="G40" s="33"/>
+      <c r="H40" s="33"/>
+      <c r="I40" s="33"/>
+      <c r="J40" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A2:A12"/>
-    <mergeCell ref="A13:A18"/>
-    <mergeCell ref="C18:J18"/>
-    <mergeCell ref="A20:A24"/>
-    <mergeCell ref="B30:B39"/>
-    <mergeCell ref="C30:J39"/>
+    <mergeCell ref="A13:A19"/>
+    <mergeCell ref="C19:J19"/>
+    <mergeCell ref="A21:A25"/>
+    <mergeCell ref="B31:B40"/>
+    <mergeCell ref="C31:J40"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
